--- a/artfynd/A 42629-2019 artfynd.xlsx
+++ b/artfynd/A 42629-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
